--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK CACTUS BUCK.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK CACTUS BUCK.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$2</definedName>
@@ -643,7 +643,11 @@
           <t>37.0</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
           <t>8.3</t>

--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK CACTUS BUCK.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 DEER BUCK CACTUS BUCK.xlsx
@@ -1,60 +1,158 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler\Desktop\GitHub\HUNT-BUILDER\processed_data\hard_data_exports\hunt_tables\2026\XLXS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A44AC29C-7A4F-4A87-B3DF-FD052F09265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1170" yWindow="135" windowWidth="25170" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hunt Table" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Hunt Table'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>hunt_name</t>
+  </si>
+  <si>
+    <t>hunt_code</t>
+  </si>
+  <si>
+    <t>sex_type</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>hunt_type</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>permits_2026_res</t>
+  </si>
+  <si>
+    <t>permits_2026_nr</t>
+  </si>
+  <si>
+    <t>permits_2026_total</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Harvest Prior Year</t>
+  </si>
+  <si>
+    <t>Percent Harvest Success (previous hunting season)</t>
+  </si>
+  <si>
+    <t>Average Age Harvested (previous hunting season)</t>
+  </si>
+  <si>
+    <t>Avg Days Hunted (previous hunting season)</t>
+  </si>
+  <si>
+    <t>Paunsaugunt</t>
+  </si>
+  <si>
+    <t>DB1058</t>
+  </si>
+  <si>
+    <t>Buck</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Any Legal Weapon</t>
+  </si>
+  <si>
+    <t>Cactus Buck</t>
+  </si>
+  <si>
+    <t>Nov 02 2026 - Nov 20 2026</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>37.0</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="8"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B301B"/>
+        <fgColor rgb="FF5B301B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F1E8"/>
+        <fgColor rgb="FFF7F1E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,131 +166,49 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C58F61"/>
+        <color rgb="FFC58F61"/>
       </left>
       <right style="thin">
-        <color rgb="00C58F61"/>
+        <color rgb="FFC58F61"/>
       </right>
       <top style="thin">
-        <color rgb="00C58F61"/>
+        <color rgb="FFC58F61"/>
       </top>
       <bottom style="thin">
-        <color rgb="00C58F61"/>
+        <color rgb="FFC58F61"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HUNT_TABLE" displayName="HUNT_TABLE" ref="A1:O2" headerRowCount="1">
-  <autoFilter ref="A1:O2"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="hunt_name"/>
-    <tableColumn id="2" name="hunt_code"/>
-    <tableColumn id="3" name="sex_type"/>
-    <tableColumn id="4" name="species"/>
-    <tableColumn id="5" name="weapon"/>
-    <tableColumn id="6" name="hunt_type"/>
-    <tableColumn id="7" name="season"/>
-    <tableColumn id="8" name="permits_2026_res"/>
-    <tableColumn id="9" name="permits_2026_nr"/>
-    <tableColumn id="10" name="permits_2026_total"/>
-    <tableColumn id="11" name="NOTES"/>
-    <tableColumn id="12" name="Harvest Prior Year"/>
-    <tableColumn id="13" name="Percent Harvest Success (previous hunting season)"/>
-    <tableColumn id="14" name="Average Age Harvested (previous hunting season)"/>
-    <tableColumn id="15" name="Avg Days Hunted (previous hunting season)"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -479,188 +495,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="15" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>hunt_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>hunt_code</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sex_type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>species</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>hunt_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>permits_2026_res</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>permits_2026_nr</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>permits_2026_total</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Harvest Prior Year</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Percent Harvest Success (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Days Hunted (previous hunting season)</t>
-        </is>
+    <row r="1" spans="1:15" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Paunsaugunt</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>DB1058</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Buck</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Deer</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Any Legal Weapon</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Cactus Buck</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Nov 02 2026 - Nov 20 2026</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
+    <row r="2" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15" right="0.15" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="5" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+  <pageSetup paperSize="5" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>